--- a/data-template.xlsx
+++ b/data-template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="11950" windowHeight="12080"/>
+    <workbookView windowWidth="24750" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="公司" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="623">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="624">
   <si>
     <t>ID</t>
   </si>
@@ -164,117 +164,16 @@
     <t>left</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>先导智能成立于</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Cambria"/>
-        <charset val="1"/>
-      </rPr>
-      <t>2002</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>年，是全球领先的新能源智能制造解决方案服务商，业务涵盖锂电池智能装备、光伏智能装备、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Cambria"/>
-        <charset val="1"/>
-      </rPr>
-      <t>3C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>智能装备、智能物流系统、氢能装备等领域，累计获得授权专利超</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Cambria"/>
-        <charset val="1"/>
-      </rPr>
-      <t>3300</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>项。</t>
-    </r>
+    <t>先导智能成立于2002年，是全球领先的新能源智能制造解决方案服务商，业务涵盖锂电池智能装备、光伏智能装备、3C智能装备、智能物流系统、氢能装备等领域，累计获得授权专利超3300项。</t>
   </si>
   <si>
     <t>Founded in 2002, Lead Intelligent is a global leader in new energy intelligent manufacturing solutions, covering lithium battery equipment, PV equipment, 3C equipment, intelligent logistics, and hydrogen energy equipment, with over 3,300 authorized patents.</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>锂电池整线装备已实现全球市占率第一，光伏串焊机累计交付超</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Cambria"/>
-        <charset val="1"/>
-      </rPr>
-      <t>30GW</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，智能物流系统进入规模化推广阶段。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Cambria"/>
-        <charset val="1"/>
-      </rPr>
-      <t>Lithium battery</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">整线 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Cambria"/>
-        <charset val="1"/>
-      </rPr>
-      <t>equipment ranks first globally in market share, PV stringer deliveries exceed 30GW, intelligent logistics system enters large-scale promotion phase.</t>
-    </r>
+    <t>锂电池整线装备已实现全球市占率第一，光伏串焊机累计交付超30GW，智能物流系统进入规模化推广阶段。</t>
+  </si>
+  <si>
+    <t>Lithium battery整线 equipment ranks first globally in market share, PV stringer deliveries exceed 30GW, intelligent logistics system enters large-scale promotion phase.</t>
   </si>
   <si>
     <t>wuliaoshaicha,youxugongliao,shijuedingwei,luoshuaningsuo,biaomianhuahen</t>
@@ -304,6 +203,9 @@
     <t>quexianjiance</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>aotewei</t>
   </si>
   <si>
@@ -322,59 +224,13 @@
     <t>dingweiduiqi,quexianjiance,zhinengmaduo</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>奥特维创立于</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Cambria"/>
-        <charset val="1"/>
-      </rPr>
-      <t>2010</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>年，是光伏、锂电和半导体专业领域知名的智能装备制造商，产品覆盖光伏产业链的拉棒、硅片、电池、组件四大环节，核心产品串焊机、硅片分选机市场占有率高。</t>
-    </r>
+    <t>奥特维创立于2010年，是光伏、锂电和半导体专业领域知名的智能装备制造商，产品覆盖光伏产业链的拉棒、硅片、电池、组件四大环节，核心产品串焊机、硅片分选机市场占有率高。</t>
   </si>
   <si>
     <t>Founded in 2010, Autowell is a renowned intelligent equipment manufacturer in PV, lithium battery and semiconductor fields, covering all four segments of PV industry chain, with core products stringer and wafer sorter holding high market share.</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>光伏串焊机全球出货量领先，半导体键合设备已获批量订单，锂电模组</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Cambria"/>
-        <charset val="1"/>
-      </rPr>
-      <t>PACK</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>生产线持续放量。</t>
-    </r>
+    <t>光伏串焊机全球出货量领先，半导体键合设备已获批量订单，锂电模组PACK生产线持续放量。</t>
   </si>
   <si>
     <t>PV stringer global shipments lead the market, semiconductor bonding equipment has received batch orders, lithium battery module PACK production line continues to scale up.</t>
@@ -410,107 +266,13 @@
     <t>dingweiduiqi,lianjieguding,xingneng</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>信捷电气成立于</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Cambria"/>
-        <charset val="1"/>
-      </rPr>
-      <t>2008</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>年，专注工业自动化控制产品的研发、生产和销售，是国内工业自动化控制领域的领军企业，主营</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Cambria"/>
-        <charset val="1"/>
-      </rPr>
-      <t>PLC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、伺服系统、人机界面、机器视觉等产品，小型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Cambria"/>
-        <charset val="1"/>
-      </rPr>
-      <t>PLC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>市占率国产第一。</t>
-    </r>
+    <t>信捷电气成立于2008年，专注工业自动化控制产品的研发、生产和销售，是国内工业自动化控制领域的领军企业，主营PLC、伺服系统、人机界面、机器视觉等产品，小型PLC市占率国产第一。</t>
   </si>
   <si>
     <t>Founded in 2008, Xinje Electric focuses on R&amp;D, production and sales of industrial automation control products, a leading domestic enterprise in industrial automation, with main products including PLC, servo systems, HMI, and machine vision, ranking first among domestic brands in small PLC market share.</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>中型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Cambria"/>
-        <charset val="1"/>
-      </rPr>
-      <t>PLC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>已实现销售收入，大型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Cambria"/>
-        <charset val="1"/>
-      </rPr>
-      <t>PLC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>研发持续推进，与华为云合作打造具身智能标杆项目。</t>
-    </r>
+    <t>中型PLC已实现销售收入，大型PLC研发持续推进，与华为云合作打造具身智能标杆项目。</t>
   </si>
   <si>
     <t>Medium PLC has achieved sales revenue, large PLC R&amp;D continues to advance, cooperating with Huawei Cloud to build embodied intelligence benchmark projects.</t>
@@ -525,6 +287,39 @@
     <t>xingneng</t>
   </si>
   <si>
+    <t>shuangliang</t>
+  </si>
+  <si>
+    <t>双良节能系统股份有限公司</t>
+  </si>
+  <si>
+    <t>Shuangliang Energy Saving System Co.</t>
+  </si>
+  <si>
+    <t>节能装备</t>
+  </si>
+  <si>
+    <t>Energy Saving Equipment</t>
+  </si>
+  <si>
+    <t>lianjieguding,xingneng,quexianjiance</t>
+  </si>
+  <si>
+    <t>双良节能是节能环保装备领域的领军企业，主营溴化锂冷热机组、换热器、空冷器等节能装备，以及多晶硅还原炉、光伏组件等新能源装备，在节能节水领域具有深厚的技术积累。</t>
+  </si>
+  <si>
+    <t>Shuangliang is a leading enterprise in energy-saving and environmental protection equipment, mainly engaged in lithium bromide chillers, heat exchangers, air coolers and other energy-saving equipment, as well as polysilicon reduction furnaces, PV modules and other new energy equipment, with deep technical accumulation in energy saving and water conservation.</t>
+  </si>
+  <si>
+    <t>多晶硅还原炉市场占有率领先，光伏组件业务快速放量，节能装备持续技术迭代。</t>
+  </si>
+  <si>
+    <t>Polysilicon reduction furnace market share leads, PV module business rapidly scales up, energy-saving equipment continues technological iteration.</t>
+  </si>
+  <si>
+    <t>luoshuaningsuo,kakouguding,dianqiceshi,biaomianhuahen</t>
+  </si>
+  <si>
     <t>rilian</t>
   </si>
   <si>
@@ -543,155 +338,13 @@
     <t>quexianjiance,wusunjiance,xingneng</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>日联科技成立于</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Cambria"/>
-        <charset val="1"/>
-      </rPr>
-      <t>2009</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>年，是中国工业</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Cambria"/>
-        <charset val="1"/>
-      </rPr>
-      <t>X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>射线智能检测领域的龙头企业，专注于工业</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Cambria"/>
-        <charset val="1"/>
-      </rPr>
-      <t>X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>射线检测装备及核心部件</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Cambria"/>
-        <charset val="1"/>
-      </rPr>
-      <t>X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>射线源的研发、生产与销售，产品广泛应用于集成电路、新能源电池、铸件焊件等检测领域。</t>
-    </r>
+    <t>日联科技成立于2009年，是中国工业X射线智能检测领域的龙头企业，专注于工业X射线检测装备及核心部件X射线源的研发、生产与销售，产品广泛应用于集成电路、新能源电池、铸件焊件等检测领域。</t>
   </si>
   <si>
     <t>Founded in 2009, Unicomp is a leading enterprise in China's industrial X-ray intelligent inspection field, focusing on R&amp;D, production and sales of industrial X-ray inspection equipment and core components X-ray sources, widely used in IC, new energy batteries, castings and weldings inspection.</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>自研</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Cambria"/>
-        <charset val="1"/>
-      </rPr>
-      <t>160kV</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>开放式微聚焦</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Cambria"/>
-        <charset val="1"/>
-      </rPr>
-      <t>X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>射线源实现批量生产，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Cambria"/>
-        <charset val="1"/>
-      </rPr>
-      <t>0.8μm</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>级缺陷检测精度达到国际先进水平，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Cambria"/>
-        <charset val="1"/>
-      </rPr>
-      <t>AI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>检测解决方案快速落地。</t>
-    </r>
+    <t>自研160kV开放式微聚焦X射线源实现批量生产，0.8μm级缺陷检测精度达到国际先进水平，AI检测解决方案快速落地。</t>
   </si>
   <si>
     <t>Self-developed 160kV open micro-focus X-ray source achieves mass production, 0.8μm defect detection precision reaches international advanced level, AI inspection solutions are rapidly deployed.</t>
@@ -724,30 +377,7 @@
     <t>shangxiawuliao,lianjieguding,rouxingshineng</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>天奇股份成立于</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Cambria"/>
-        <charset val="1"/>
-      </rPr>
-      <t>1997</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>年，深耕汽车智能装备行业近三十年，形成了以智能装备为核心、锂电池循环和机器人产业为战略的三大产业集群，与优必选合资设立公司专注工业人形机器人商业化落地。</t>
-    </r>
+    <t>天奇股份成立于1997年，深耕汽车智能装备行业近三十年，形成了以智能装备为核心、锂电池循环和机器人产业为战略的三大产业集群，与优必选合资设立公司专注工业人形机器人商业化落地。</t>
   </si>
   <si>
     <t>Founded in 1997, Tianqi has been deeply engaged in automotive intelligent equipment for nearly 30 years, forming three industrial clusters with intelligent equipment as core, lithium battery recycling and robotics as strategic industries, jointly established a company with UBTECH focusing on commercialization of industrial humanoid robots.</t>
@@ -786,75 +416,13 @@
     <t>dingweiduiqi,quexianjiance,xingneng</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>锡华科技成立于</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Cambria"/>
-        <charset val="1"/>
-      </rPr>
-      <t>2001</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>年，主要从事大型高端装备专用部件的研发、制造与销售，产品以风电齿轮箱专用部件为主、注塑机厚大专用部件为辅，是全球领先的大型高端装备专用部件制造商。</t>
-    </r>
+    <t>锡华科技成立于2001年，主要从事大型高端装备专用部件的研发、制造与销售，产品以风电齿轮箱专用部件为主、注塑机厚大专用部件为辅，是全球领先的大型高端装备专用部件制造商。</t>
   </si>
   <si>
     <t>Founded in 2001, Xihua specializes in R&amp;D, manufacturing and sales of large high-end equipment components, mainly wind turbine gearbox components and injection molding machine thick components, a globally leading manufacturer of large high-end equipment components.</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>风电齿轮箱专用部件全球市场占有率约</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Cambria"/>
-        <charset val="1"/>
-      </rPr>
-      <t>20%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Cambria"/>
-        <charset val="1"/>
-      </rPr>
-      <t>IPO</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>募投项目聚焦于产能扩张与研发中心建设。</t>
-    </r>
+    <t>风电齿轮箱专用部件全球市场占有率约20%，IPO募投项目聚焦于产能扩张与研发中心建设。</t>
   </si>
   <si>
     <t>Wind turbine gearbox components global market share is about 20%, IPO fundraising projects focus on capacity expansion and R&amp;D center construction.</t>
@@ -881,6 +449,9 @@
     <t>dingweiduiqi,lianjieguding,wusunjiance</t>
   </si>
   <si>
+    <t>right</t>
+  </si>
+  <si>
     <t>派克新材是一家专业从事金属锻件的研发、生产和销售的高新技术企业，主营产品涵盖辗制环形锻件、自由锻件、精密模锻件等，广泛应用于航空、航天、电力、石化等高端领域，是航空航天特种合金锻件的重要供应商。</t>
   </si>
   <si>
@@ -914,31 +485,13 @@
     <t>dingweiduiqi,xingneng,quexianjiance</t>
   </si>
   <si>
-    <t>right</t>
-  </si>
-  <si>
     <t>德力佳是全球领先的风电齿轮箱龙头企业，专注于风电齿轮箱的研发、制造与销售，产品广泛应用于陆上风电和海上风电领域，为全球主要风电整机制造商提供核心传动部件。</t>
   </si>
   <si>
     <t>Delijia is a global leading wind turbine gearbox enterprise, focusing on R&amp;D, manufacturing and sales of wind turbine gearboxes, products widely used in onshore and offshore wind power, providing core transmission components for major global wind turbine manufacturers.</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Cambria"/>
-        <charset val="1"/>
-      </rPr>
-      <t>IPO</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>募资用于风电核心装备产业化项目和研发中心建设，巩固全球市场竞争力。</t>
-    </r>
+    <t>IPO募资用于风电核心装备产业化项目和研发中心建设，巩固全球市场竞争力。</t>
   </si>
   <si>
     <t>IPO fundraising is used for wind power core equipment industrialization project and R&amp;D center construction, consolidating global market competitiveness.</t>
@@ -965,30 +518,7 @@
     <t>dingweiduiqi,quexianjiance,wusunjiance</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>航亚科技专注于航空发动机精密零部件的研发、制造与销售，产品主要为航空发动机叶片、叶盘等关键部件，已进入</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Cambria"/>
-        <charset val="1"/>
-      </rPr>
-      <t>GE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>航空、罗罗等国际航空发动机巨头的供应链体系。</t>
-    </r>
+    <t>航亚科技专注于航空发动机精密零部件的研发、制造与销售，产品主要为航空发动机叶片、叶盘等关键部件，已进入GE航空、罗罗等国际航空发动机巨头的供应链体系。</t>
   </si>
   <si>
     <t>Hangya Technology focuses on R&amp;D, manufacturing and sales of aero engine precision components, mainly aero engine blades and blisks, having entered the supply chain systems of GE Aviation, Rolls-Royce and other international aero engine giants.</t>
@@ -1039,30 +569,7 @@
     <t>微导纳米科技股份有限公司</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Cambria"/>
-        <charset val="1"/>
-      </rPr>
-      <t>Wuxi Micro</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">导 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Cambria"/>
-        <charset val="1"/>
-      </rPr>
-      <t>Nano Technology Co.</t>
-    </r>
+    <t>Wuxi Micro导 Nano Technology Co.</t>
   </si>
   <si>
     <t>半导体设备</t>
@@ -1071,98 +578,13 @@
     <t>Semiconductor Equipment</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>微导纳米专注于半导体、光伏领域薄膜沉积设备的研发、生产和销售，核心产品包括</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Cambria"/>
-        <charset val="1"/>
-      </rPr>
-      <t>ALD</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Cambria"/>
-        <charset val="1"/>
-      </rPr>
-      <t>CVD</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>等设备，在半导体先进制程和光伏电池片制造领域具有领先的技术优势。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Cambria"/>
-        <charset val="1"/>
-      </rPr>
-      <t>Micro</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">导 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Cambria"/>
-        <charset val="1"/>
-      </rPr>
-      <t>Nano focuses on R&amp;D, production and sales of thin film deposition equipment for semiconductor and PV fields, core products include ALD, CVD equipment, with leading technical advantages in advanced semiconductor processes and PV cell manufacturing.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>半导体</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Cambria"/>
-        <charset val="1"/>
-      </rPr>
-      <t>ALD</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>设备进入主流晶圆厂验证，光伏设备持续迭代升级，可转债募资加码半导体设备领域。</t>
-    </r>
+    <t>微导纳米专注于半导体、光伏领域薄膜沉积设备的研发、生产和销售，核心产品包括ALD、CVD等设备，在半导体先进制程和光伏电池片制造领域具有领先的技术优势。</t>
+  </si>
+  <si>
+    <t>Micro导 Nano focuses on R&amp;D, production and sales of thin film deposition equipment for semiconductor and PV fields, core products include ALD, CVD equipment, with leading technical advantages in advanced semiconductor processes and PV cell manufacturing.</t>
+  </si>
+  <si>
+    <t>半导体ALD设备进入主流晶圆厂验证，光伏设备持续迭代升级，可转债募资加码半导体设备领域。</t>
   </si>
   <si>
     <t>Semiconductor ALD equipment enters mainstream wafer fab verification, PV equipment continues to upgrade, convertible bond fundraising increases investment in semiconductor equipment field.</t>
@@ -1171,39 +593,6 @@
     <t>shijuedingwei,biaomianhuahen,dianqiceshi</t>
   </si>
   <si>
-    <t>shuangliang</t>
-  </si>
-  <si>
-    <t>双良节能系统股份有限公司</t>
-  </si>
-  <si>
-    <t>Shuangliang Energy Saving System Co.</t>
-  </si>
-  <si>
-    <t>节能装备</t>
-  </si>
-  <si>
-    <t>Energy Saving Equipment</t>
-  </si>
-  <si>
-    <t>lianjieguding,xingneng,quexianjiance</t>
-  </si>
-  <si>
-    <t>双良节能是节能环保装备领域的领军企业，主营溴化锂冷热机组、换热器、空冷器等节能装备，以及多晶硅还原炉、光伏组件等新能源装备，在节能节水领域具有深厚的技术积累。</t>
-  </si>
-  <si>
-    <t>Shuangliang is a leading enterprise in energy-saving and environmental protection equipment, mainly engaged in lithium bromide chillers, heat exchangers, air coolers and other energy-saving equipment, as well as polysilicon reduction furnaces, PV modules and other new energy equipment, with deep technical accumulation in energy saving and water conservation.</t>
-  </si>
-  <si>
-    <t>多晶硅还原炉市场占有率领先，光伏组件业务快速放量，节能装备持续技术迭代。</t>
-  </si>
-  <si>
-    <t>Polysilicon reduction furnace market share leads, PV module business rapidly scales up, energy-saving equipment continues technological iteration.</t>
-  </si>
-  <si>
-    <t>luoshuaningsuo,kakouguding,dianqiceshi,biaomianhuahen</t>
-  </si>
-  <si>
     <t>huadong</t>
   </si>
   <si>
@@ -1294,30 +683,7 @@
     <t>Medical Equipment</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>祥生医疗是专业从事超声医学影像设备研发、制造和销售的高新技术企业，被誉为科创板超声第一股，产品涵盖便携式超声、台式超声、智能超声等，远销全球</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Cambria"/>
-        <charset val="1"/>
-      </rPr>
-      <t>100</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>多个国家和地区。</t>
-    </r>
+    <t>祥生医疗是专业从事超声医学影像设备研发、制造和销售的高新技术企业，被誉为科创板超声第一股，产品涵盖便携式超声、台式超声、智能超声等，远销全球100多个国家和地区。</t>
   </si>
   <si>
     <t>Xiangsheng is a high-tech enterprise specializing in R&amp;D, manufacturing and sales of ultrasound medical imaging equipment, known as the first ultrasound stock on STAR Market, products cover portable ultrasound, desktop ultrasound, intelligent ultrasound, exported to over 100 countries and regions.</t>
@@ -2551,23 +1917,13 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="21">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Cambria"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Noto Sans CJK SC"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -2915,27 +2271,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD0D0D0"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD0D0D0"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD0D0D0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD0D0D0"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -3039,19 +2380,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3060,138 +2410,123 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3708,1352 +3043,1526 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" ht="36" spans="1:33">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:33">
+      <c r="A2" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>35</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" t="s">
         <v>36</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" t="s">
         <v>37</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" t="s">
         <v>38</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" t="s">
         <v>39</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" t="s">
         <v>39</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" t="s">
         <v>40</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" t="s">
         <v>41</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" t="s">
         <v>42</v>
       </c>
-      <c r="L2" s="1">
+      <c r="L2">
         <v>0</v>
       </c>
-      <c r="M2" s="1">
+      <c r="M2">
         <v>92</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" t="s">
         <v>43</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="O2" t="s">
         <v>44</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" t="s">
         <v>45</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="Q2" t="s">
         <v>46</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="R2" t="s">
         <v>47</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="S2" t="s">
         <v>48</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="T2" t="s">
         <v>49</v>
       </c>
-      <c r="U2" s="1">
+      <c r="U2">
         <v>100</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="V2" t="s">
         <v>50</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="W2" t="s">
         <v>51</v>
       </c>
-      <c r="X2" s="1">
+      <c r="X2">
         <v>95</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="Y2" t="s">
         <v>52</v>
       </c>
-      <c r="Z2" s="1" t="s">
+      <c r="Z2" t="s">
         <v>53</v>
       </c>
-      <c r="AA2" s="1">
+      <c r="AA2">
         <v>90</v>
       </c>
-      <c r="AB2" s="1" t="s">
+      <c r="AB2" t="s">
         <v>54</v>
       </c>
-      <c r="AC2" s="1" t="s">
+      <c r="AC2" t="s">
         <v>55</v>
       </c>
-      <c r="AD2" s="1">
+      <c r="AD2">
         <v>88</v>
       </c>
-      <c r="AE2" s="1"/>
-      <c r="AF2" s="1"/>
-      <c r="AG2" s="1"/>
-    </row>
-    <row r="3" ht="36" spans="1:33">
-      <c r="A3" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="AE2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33">
+      <c r="A3" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="B3" t="s">
         <v>58</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="C3" t="s">
         <v>59</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="D3" t="s">
         <v>60</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="E3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F3" t="s">
         <v>38</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" t="s">
         <v>39</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" t="s">
         <v>39</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" t="s">
         <v>40</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="K3" s="1" t="s">
+      <c r="J3" t="s">
+        <v>62</v>
+      </c>
+      <c r="K3" t="s">
         <v>42</v>
       </c>
-      <c r="L3" s="1">
+      <c r="L3">
         <v>1</v>
       </c>
-      <c r="M3" s="1">
+      <c r="M3">
         <v>88</v>
       </c>
-      <c r="N3" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="O3" s="1" t="s">
+      <c r="N3" t="s">
         <v>63</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="O3" t="s">
         <v>64</v>
       </c>
-      <c r="Q3" s="1" t="s">
+      <c r="P3" t="s">
         <v>65</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="Q3" t="s">
         <v>66</v>
       </c>
-      <c r="S3" s="1" t="s">
+      <c r="R3" t="s">
+        <v>67</v>
+      </c>
+      <c r="S3" t="s">
         <v>50</v>
       </c>
-      <c r="T3" s="1" t="s">
+      <c r="T3" t="s">
         <v>51</v>
       </c>
-      <c r="U3" s="1">
+      <c r="U3">
         <v>100</v>
       </c>
-      <c r="V3" s="1" t="s">
+      <c r="V3" t="s">
         <v>54</v>
       </c>
-      <c r="W3" s="1" t="s">
+      <c r="W3" t="s">
         <v>55</v>
       </c>
-      <c r="X3" s="1">
+      <c r="X3">
         <v>95</v>
       </c>
-      <c r="Y3" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z3" s="1" t="s">
+      <c r="Y3" t="s">
         <v>68</v>
       </c>
-      <c r="AA3" s="1">
+      <c r="Z3" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA3">
         <v>85</v>
       </c>
-      <c r="AB3" s="1"/>
-      <c r="AC3" s="1"/>
-      <c r="AD3" s="1"/>
-      <c r="AE3" s="1"/>
-      <c r="AF3" s="1"/>
-      <c r="AG3" s="1"/>
-    </row>
-    <row r="4" ht="46" spans="1:33">
-      <c r="A4" s="1" t="s">
+      <c r="AB3" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>56</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>56</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33">
+      <c r="A4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I4" t="s">
+        <v>75</v>
+      </c>
+      <c r="J4" t="s">
+        <v>76</v>
+      </c>
+      <c r="K4" t="s">
+        <v>42</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>75</v>
+      </c>
+      <c r="N4" t="s">
+        <v>77</v>
+      </c>
+      <c r="O4" t="s">
+        <v>78</v>
+      </c>
+      <c r="P4" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>80</v>
+      </c>
+      <c r="R4" t="s">
+        <v>81</v>
+      </c>
+      <c r="S4" t="s">
+        <v>50</v>
+      </c>
+      <c r="T4" t="s">
+        <v>51</v>
+      </c>
+      <c r="U4">
+        <v>100</v>
+      </c>
+      <c r="V4" t="s">
+        <v>52</v>
+      </c>
+      <c r="W4" t="s">
+        <v>53</v>
+      </c>
+      <c r="X4">
+        <v>85</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>83</v>
+      </c>
+      <c r="AA4">
+        <v>80</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33">
+      <c r="A5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D5" t="s">
+        <v>87</v>
+      </c>
+      <c r="E5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I5" t="s">
+        <v>40</v>
+      </c>
+      <c r="J5" t="s">
+        <v>89</v>
+      </c>
+      <c r="K5" t="s">
+        <v>42</v>
+      </c>
+      <c r="L5">
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <v>86</v>
+      </c>
+      <c r="N5" t="s">
+        <v>90</v>
+      </c>
+      <c r="O5" t="s">
+        <v>91</v>
+      </c>
+      <c r="P5" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>93</v>
+      </c>
+      <c r="R5" t="s">
+        <v>94</v>
+      </c>
+      <c r="S5" t="s">
+        <v>52</v>
+      </c>
+      <c r="T5" t="s">
+        <v>53</v>
+      </c>
+      <c r="U5">
+        <v>100</v>
+      </c>
+      <c r="V5" t="s">
+        <v>82</v>
+      </c>
+      <c r="W5" t="s">
+        <v>83</v>
+      </c>
+      <c r="X5">
+        <v>95</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA5">
+        <v>90</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>56</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>56</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33">
+      <c r="A6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E6" t="s">
+        <v>99</v>
+      </c>
+      <c r="F6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" t="s">
+        <v>75</v>
+      </c>
+      <c r="J6" t="s">
+        <v>100</v>
+      </c>
+      <c r="K6" t="s">
+        <v>42</v>
+      </c>
+      <c r="L6">
+        <v>4</v>
+      </c>
+      <c r="M6">
+        <v>82</v>
+      </c>
+      <c r="N6" t="s">
+        <v>101</v>
+      </c>
+      <c r="O6" t="s">
+        <v>102</v>
+      </c>
+      <c r="P6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>104</v>
+      </c>
+      <c r="R6" t="s">
+        <v>105</v>
+      </c>
+      <c r="S6" t="s">
+        <v>54</v>
+      </c>
+      <c r="T6" t="s">
+        <v>55</v>
+      </c>
+      <c r="U6">
+        <v>100</v>
+      </c>
+      <c r="V6" t="s">
+        <v>106</v>
+      </c>
+      <c r="W6" t="s">
+        <v>107</v>
+      </c>
+      <c r="X6">
+        <v>95</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>83</v>
+      </c>
+      <c r="AA6">
+        <v>85</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33">
+      <c r="A7" t="s">
+        <v>108</v>
+      </c>
+      <c r="B7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D7" t="s">
+        <v>111</v>
+      </c>
+      <c r="E7" t="s">
+        <v>112</v>
+      </c>
+      <c r="F7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" t="s">
+        <v>75</v>
+      </c>
+      <c r="J7" t="s">
+        <v>113</v>
+      </c>
+      <c r="K7" t="s">
+        <v>42</v>
+      </c>
+      <c r="L7">
+        <v>5</v>
+      </c>
+      <c r="M7">
+        <v>78</v>
+      </c>
+      <c r="N7" t="s">
+        <v>114</v>
+      </c>
+      <c r="O7" t="s">
+        <v>115</v>
+      </c>
+      <c r="P7" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>117</v>
+      </c>
+      <c r="R7" t="s">
+        <v>118</v>
+      </c>
+      <c r="S7" t="s">
+        <v>48</v>
+      </c>
+      <c r="T7" t="s">
+        <v>49</v>
+      </c>
+      <c r="U7">
+        <v>100</v>
+      </c>
+      <c r="V7" t="s">
+        <v>52</v>
+      </c>
+      <c r="W7" t="s">
+        <v>53</v>
+      </c>
+      <c r="X7">
+        <v>90</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>119</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>120</v>
+      </c>
+      <c r="AA7">
+        <v>75</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>56</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>56</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33">
+      <c r="A8" t="s">
+        <v>121</v>
+      </c>
+      <c r="B8" t="s">
+        <v>122</v>
+      </c>
+      <c r="C8" t="s">
+        <v>123</v>
+      </c>
+      <c r="D8" t="s">
+        <v>124</v>
+      </c>
+      <c r="E8" t="s">
+        <v>125</v>
+      </c>
+      <c r="F8" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" t="s">
+        <v>39</v>
+      </c>
+      <c r="H8" t="s">
+        <v>39</v>
+      </c>
+      <c r="I8" t="s">
+        <v>75</v>
+      </c>
+      <c r="J8" t="s">
+        <v>126</v>
+      </c>
+      <c r="K8" t="s">
+        <v>42</v>
+      </c>
+      <c r="L8">
+        <v>6</v>
+      </c>
+      <c r="M8">
+        <v>70</v>
+      </c>
+      <c r="N8" t="s">
+        <v>127</v>
+      </c>
+      <c r="O8" t="s">
+        <v>128</v>
+      </c>
+      <c r="P8" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>130</v>
+      </c>
+      <c r="R8" t="s">
+        <v>131</v>
+      </c>
+      <c r="S8" t="s">
+        <v>50</v>
+      </c>
+      <c r="T8" t="s">
+        <v>51</v>
+      </c>
+      <c r="U8">
+        <v>100</v>
+      </c>
+      <c r="V8" t="s">
+        <v>54</v>
+      </c>
+      <c r="W8" t="s">
+        <v>55</v>
+      </c>
+      <c r="X8">
+        <v>90</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>83</v>
+      </c>
+      <c r="AA8">
+        <v>85</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>56</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>56</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33">
+      <c r="A9" t="s">
+        <v>132</v>
+      </c>
+      <c r="B9" t="s">
+        <v>133</v>
+      </c>
+      <c r="C9" t="s">
+        <v>134</v>
+      </c>
+      <c r="D9" t="s">
+        <v>135</v>
+      </c>
+      <c r="E9" t="s">
+        <v>136</v>
+      </c>
+      <c r="F9" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9" t="s">
+        <v>39</v>
+      </c>
+      <c r="I9" t="s">
+        <v>75</v>
+      </c>
+      <c r="J9" t="s">
+        <v>137</v>
+      </c>
+      <c r="K9" t="s">
+        <v>138</v>
+      </c>
+      <c r="L9">
+        <v>8</v>
+      </c>
+      <c r="M9">
+        <v>85</v>
+      </c>
+      <c r="N9" t="s">
+        <v>139</v>
+      </c>
+      <c r="O9" t="s">
+        <v>140</v>
+      </c>
+      <c r="P9" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>142</v>
+      </c>
+      <c r="R9" t="s">
+        <v>143</v>
+      </c>
+      <c r="S9" t="s">
+        <v>50</v>
+      </c>
+      <c r="T9" t="s">
+        <v>51</v>
+      </c>
+      <c r="U9">
+        <v>100</v>
+      </c>
+      <c r="V9" t="s">
+        <v>52</v>
+      </c>
+      <c r="W9" t="s">
+        <v>53</v>
+      </c>
+      <c r="X9">
+        <v>95</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>106</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>107</v>
+      </c>
+      <c r="AA9">
+        <v>90</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>56</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>56</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33">
+      <c r="A10" t="s">
+        <v>144</v>
+      </c>
+      <c r="B10" t="s">
+        <v>145</v>
+      </c>
+      <c r="C10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D10" t="s">
+        <v>147</v>
+      </c>
+      <c r="E10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F10" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" t="s">
+        <v>39</v>
+      </c>
+      <c r="I10" t="s">
+        <v>75</v>
+      </c>
+      <c r="J10" t="s">
+        <v>149</v>
+      </c>
+      <c r="K10" t="s">
+        <v>138</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>72</v>
+      </c>
+      <c r="N10" t="s">
+        <v>150</v>
+      </c>
+      <c r="O10" t="s">
+        <v>151</v>
+      </c>
+      <c r="P10" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>153</v>
+      </c>
+      <c r="R10" t="s">
+        <v>154</v>
+      </c>
+      <c r="S10" t="s">
+        <v>50</v>
+      </c>
+      <c r="T10" t="s">
+        <v>51</v>
+      </c>
+      <c r="U10">
+        <v>100</v>
+      </c>
+      <c r="V10" t="s">
+        <v>82</v>
+      </c>
+      <c r="W10" t="s">
+        <v>83</v>
+      </c>
+      <c r="X10">
+        <v>90</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA10">
+        <v>85</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>56</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>56</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33">
+      <c r="A11" t="s">
+        <v>155</v>
+      </c>
+      <c r="B11" t="s">
+        <v>156</v>
+      </c>
+      <c r="C11" t="s">
+        <v>157</v>
+      </c>
+      <c r="D11" t="s">
+        <v>158</v>
+      </c>
+      <c r="E11" t="s">
+        <v>159</v>
+      </c>
+      <c r="F11" t="s">
+        <v>38</v>
+      </c>
+      <c r="G11" t="s">
+        <v>39</v>
+      </c>
+      <c r="H11" t="s">
+        <v>39</v>
+      </c>
+      <c r="I11" t="s">
+        <v>75</v>
+      </c>
+      <c r="J11" t="s">
+        <v>160</v>
+      </c>
+      <c r="K11" t="s">
+        <v>138</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>80</v>
+      </c>
+      <c r="N11" t="s">
+        <v>161</v>
+      </c>
+      <c r="O11" t="s">
+        <v>162</v>
+      </c>
+      <c r="P11" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>164</v>
+      </c>
+      <c r="R11" t="s">
+        <v>165</v>
+      </c>
+      <c r="S11" t="s">
+        <v>50</v>
+      </c>
+      <c r="T11" t="s">
+        <v>51</v>
+      </c>
+      <c r="U11">
+        <v>100</v>
+      </c>
+      <c r="V11" t="s">
+        <v>54</v>
+      </c>
+      <c r="W11" t="s">
+        <v>55</v>
+      </c>
+      <c r="X11">
+        <v>95</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>106</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>107</v>
+      </c>
+      <c r="AA11">
+        <v>90</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>56</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>56</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33">
+      <c r="A12" t="s">
+        <v>166</v>
+      </c>
+      <c r="B12" t="s">
+        <v>167</v>
+      </c>
+      <c r="C12" t="s">
+        <v>168</v>
+      </c>
+      <c r="D12" t="s">
+        <v>169</v>
+      </c>
+      <c r="E12" t="s">
+        <v>170</v>
+      </c>
+      <c r="F12" t="s">
+        <v>38</v>
+      </c>
+      <c r="G12" t="s">
+        <v>39</v>
+      </c>
+      <c r="H12" t="s">
+        <v>39</v>
+      </c>
+      <c r="I12" t="s">
+        <v>75</v>
+      </c>
+      <c r="J12" t="s">
+        <v>76</v>
+      </c>
+      <c r="K12" t="s">
+        <v>138</v>
+      </c>
+      <c r="L12">
+        <v>2</v>
+      </c>
+      <c r="M12">
+        <v>76</v>
+      </c>
+      <c r="N12" t="s">
+        <v>171</v>
+      </c>
+      <c r="O12" t="s">
+        <v>172</v>
+      </c>
+      <c r="P12" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>174</v>
+      </c>
+      <c r="R12" t="s">
+        <v>175</v>
+      </c>
+      <c r="S12" t="s">
+        <v>50</v>
+      </c>
+      <c r="T12" t="s">
+        <v>51</v>
+      </c>
+      <c r="U12">
+        <v>100</v>
+      </c>
+      <c r="V12" t="s">
+        <v>52</v>
+      </c>
+      <c r="W12" t="s">
+        <v>53</v>
+      </c>
+      <c r="X12">
+        <v>90</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>83</v>
+      </c>
+      <c r="AA12">
+        <v>85</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>56</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>56</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33">
+      <c r="A13" t="s">
+        <v>176</v>
+      </c>
+      <c r="B13" t="s">
+        <v>177</v>
+      </c>
+      <c r="C13" t="s">
+        <v>178</v>
+      </c>
+      <c r="D13" t="s">
+        <v>179</v>
+      </c>
+      <c r="E13" t="s">
+        <v>180</v>
+      </c>
+      <c r="F13" t="s">
+        <v>38</v>
+      </c>
+      <c r="G13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H13" t="s">
+        <v>39</v>
+      </c>
+      <c r="I13" t="s">
+        <v>75</v>
+      </c>
+      <c r="J13" t="s">
+        <v>126</v>
+      </c>
+      <c r="K13" t="s">
+        <v>138</v>
+      </c>
+      <c r="L13">
+        <v>3</v>
+      </c>
+      <c r="M13">
+        <v>74</v>
+      </c>
+      <c r="N13" t="s">
+        <v>181</v>
+      </c>
+      <c r="O13" t="s">
+        <v>182</v>
+      </c>
+      <c r="P13" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>184</v>
+      </c>
+      <c r="R13" t="s">
+        <v>185</v>
+      </c>
+      <c r="S13" t="s">
+        <v>50</v>
+      </c>
+      <c r="T13" t="s">
+        <v>51</v>
+      </c>
+      <c r="U13">
+        <v>100</v>
+      </c>
+      <c r="V13" t="s">
+        <v>54</v>
+      </c>
+      <c r="W13" t="s">
+        <v>55</v>
+      </c>
+      <c r="X13">
+        <v>90</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>83</v>
+      </c>
+      <c r="AA13">
+        <v>85</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>56</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF13" t="s">
+        <v>56</v>
+      </c>
+      <c r="AG13" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33">
+      <c r="A14" t="s">
+        <v>186</v>
+      </c>
+      <c r="B14" t="s">
+        <v>187</v>
+      </c>
+      <c r="C14" t="s">
+        <v>188</v>
+      </c>
+      <c r="D14" t="s">
+        <v>189</v>
+      </c>
+      <c r="E14" t="s">
+        <v>190</v>
+      </c>
+      <c r="F14" t="s">
+        <v>38</v>
+      </c>
+      <c r="G14" t="s">
+        <v>39</v>
+      </c>
+      <c r="H14" t="s">
+        <v>39</v>
+      </c>
+      <c r="I14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J14" t="s">
+        <v>192</v>
+      </c>
+      <c r="K14" t="s">
+        <v>138</v>
+      </c>
+      <c r="L14">
+        <v>4</v>
+      </c>
+      <c r="M14">
+        <v>35</v>
+      </c>
+      <c r="N14" t="s">
+        <v>193</v>
+      </c>
+      <c r="O14" t="s">
+        <v>194</v>
+      </c>
+      <c r="P14" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>196</v>
+      </c>
+      <c r="R14" t="s">
+        <v>197</v>
+      </c>
+      <c r="S14" t="s">
+        <v>48</v>
+      </c>
+      <c r="T14" t="s">
+        <v>49</v>
+      </c>
+      <c r="U14">
+        <v>100</v>
+      </c>
+      <c r="V14" t="s">
+        <v>198</v>
+      </c>
+      <c r="W14" t="s">
+        <v>199</v>
+      </c>
+      <c r="X14">
+        <v>80</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z14" t="s">
         <v>69</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="AA14">
+        <v>75</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>56</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>56</v>
+      </c>
+      <c r="AG14" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33">
+      <c r="A15" t="s">
+        <v>200</v>
+      </c>
+      <c r="B15" t="s">
+        <v>201</v>
+      </c>
+      <c r="C15" t="s">
+        <v>202</v>
+      </c>
+      <c r="D15" t="s">
+        <v>203</v>
+      </c>
+      <c r="E15" t="s">
+        <v>204</v>
+      </c>
+      <c r="F15" t="s">
         <v>38</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G15" t="s">
         <v>39</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H15" t="s">
         <v>39</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J4" s="1" t="s">
+      <c r="I15" t="s">
         <v>75</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L4" s="1">
-        <v>2</v>
-      </c>
-      <c r="M4" s="1">
-        <v>75</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="S4" s="1" t="s">
+      <c r="J15" t="s">
+        <v>205</v>
+      </c>
+      <c r="K15" t="s">
+        <v>138</v>
+      </c>
+      <c r="L15">
+        <v>5</v>
+      </c>
+      <c r="M15">
+        <v>68</v>
+      </c>
+      <c r="N15" t="s">
+        <v>206</v>
+      </c>
+      <c r="O15" t="s">
+        <v>207</v>
+      </c>
+      <c r="P15" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>209</v>
+      </c>
+      <c r="R15" t="s">
+        <v>210</v>
+      </c>
+      <c r="S15" t="s">
         <v>50</v>
       </c>
-      <c r="T4" s="1" t="s">
+      <c r="T15" t="s">
         <v>51</v>
       </c>
-      <c r="U4" s="1">
+      <c r="U15">
         <v>100</v>
       </c>
-      <c r="V4" s="1" t="s">
+      <c r="V15" t="s">
         <v>52</v>
       </c>
-      <c r="W4" s="1" t="s">
+      <c r="W15" t="s">
         <v>53</v>
       </c>
-      <c r="X4" s="1">
+      <c r="X15">
+        <v>90</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA15">
         <v>85</v>
       </c>
-      <c r="Y4" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="Z4" s="1" t="s">
+      <c r="AB15" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>56</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE15" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF15" t="s">
+        <v>56</v>
+      </c>
+      <c r="AG15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33">
+      <c r="A16" t="s">
+        <v>211</v>
+      </c>
+      <c r="B16" t="s">
+        <v>212</v>
+      </c>
+      <c r="C16" t="s">
+        <v>213</v>
+      </c>
+      <c r="D16" t="s">
+        <v>214</v>
+      </c>
+      <c r="E16" t="s">
+        <v>215</v>
+      </c>
+      <c r="F16" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H16" t="s">
+        <v>39</v>
+      </c>
+      <c r="I16" t="s">
+        <v>191</v>
+      </c>
+      <c r="J16" t="s">
+        <v>126</v>
+      </c>
+      <c r="K16" t="s">
+        <v>138</v>
+      </c>
+      <c r="L16">
+        <v>6</v>
+      </c>
+      <c r="M16">
+        <v>45</v>
+      </c>
+      <c r="N16" t="s">
+        <v>216</v>
+      </c>
+      <c r="O16" t="s">
+        <v>217</v>
+      </c>
+      <c r="P16" t="s">
+        <v>218</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>219</v>
+      </c>
+      <c r="R16" t="s">
+        <v>185</v>
+      </c>
+      <c r="S16" t="s">
+        <v>50</v>
+      </c>
+      <c r="T16" t="s">
+        <v>51</v>
+      </c>
+      <c r="U16">
+        <v>100</v>
+      </c>
+      <c r="V16" t="s">
+        <v>54</v>
+      </c>
+      <c r="W16" t="s">
+        <v>55</v>
+      </c>
+      <c r="X16">
+        <v>90</v>
+      </c>
+      <c r="Y16" t="s">
         <v>82</v>
       </c>
-      <c r="AA4" s="1">
-        <v>80</v>
-      </c>
-      <c r="AB4" s="1"/>
-      <c r="AC4" s="1"/>
-      <c r="AD4" s="1"/>
-      <c r="AE4" s="1"/>
-      <c r="AF4" s="1"/>
-      <c r="AG4" s="1"/>
-    </row>
-    <row r="5" ht="46" spans="1:33">
-      <c r="A5" s="1" t="s">
+      <c r="Z16" t="s">
         <v>83</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C5" s="1" t="s">
+      <c r="AA16">
         <v>85</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L5" s="1">
-        <v>3</v>
-      </c>
-      <c r="M5" s="1">
-        <v>82</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="O5" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q5" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="R5" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="S5" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="T5" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="U5" s="1">
-        <v>100</v>
-      </c>
-      <c r="V5" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="W5" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="X5" s="1">
-        <v>95</v>
-      </c>
-      <c r="Y5" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="Z5" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="AA5" s="1">
-        <v>85</v>
-      </c>
-      <c r="AB5" s="1"/>
-      <c r="AC5" s="1"/>
-      <c r="AD5" s="1"/>
-      <c r="AE5" s="1"/>
-      <c r="AF5" s="1"/>
-      <c r="AG5" s="1"/>
-    </row>
-    <row r="6" ht="46" spans="1:33">
-      <c r="A6" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L6" s="1">
-        <v>4</v>
-      </c>
-      <c r="M6" s="1">
-        <v>78</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="R6" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="S6" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="T6" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U6" s="1">
-        <v>100</v>
-      </c>
-      <c r="V6" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="W6" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="X6" s="1">
-        <v>90</v>
-      </c>
-      <c r="Y6" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="Z6" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="AA6" s="1">
-        <v>75</v>
-      </c>
-      <c r="AB6" s="1"/>
-      <c r="AC6" s="1"/>
-      <c r="AD6" s="1"/>
-      <c r="AE6" s="1"/>
-      <c r="AF6" s="1"/>
-      <c r="AG6" s="1"/>
-    </row>
-    <row r="7" ht="46" spans="1:33">
-      <c r="A7" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L7" s="1">
-        <v>5</v>
-      </c>
-      <c r="M7" s="1">
-        <v>70</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q7" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="R7" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="S7" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="T7" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="U7" s="1">
-        <v>100</v>
-      </c>
-      <c r="V7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="W7" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="X7" s="1">
-        <v>90</v>
-      </c>
-      <c r="Y7" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="Z7" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="AA7" s="1">
-        <v>85</v>
-      </c>
-      <c r="AB7" s="1"/>
-      <c r="AC7" s="1"/>
-      <c r="AD7" s="1"/>
-      <c r="AE7" s="1"/>
-      <c r="AF7" s="1"/>
-      <c r="AG7" s="1"/>
-    </row>
-    <row r="8" ht="46" spans="1:33">
-      <c r="A8" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L8" s="1">
-        <v>6</v>
-      </c>
-      <c r="M8" s="1">
-        <v>85</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="O8" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="Q8" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="R8" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="S8" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="T8" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="U8" s="1">
-        <v>100</v>
-      </c>
-      <c r="V8" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="W8" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="X8" s="1">
-        <v>95</v>
-      </c>
-      <c r="Y8" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="Z8" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="AA8" s="1">
-        <v>90</v>
-      </c>
-      <c r="AB8" s="1"/>
-      <c r="AC8" s="1"/>
-      <c r="AD8" s="1"/>
-      <c r="AE8" s="1"/>
-      <c r="AF8" s="1"/>
-      <c r="AG8" s="1"/>
-    </row>
-    <row r="9" ht="46" spans="1:33">
-      <c r="A9" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="L9" s="1">
-        <v>0</v>
-      </c>
-      <c r="M9" s="1">
-        <v>72</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="O9" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="P9" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="Q9" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="R9" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="S9" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="T9" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="U9" s="1">
-        <v>100</v>
-      </c>
-      <c r="V9" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="W9" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="X9" s="1">
-        <v>90</v>
-      </c>
-      <c r="Y9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z9" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="AA9" s="1">
-        <v>85</v>
-      </c>
-      <c r="AB9" s="1"/>
-      <c r="AC9" s="1"/>
-      <c r="AD9" s="1"/>
-      <c r="AE9" s="1"/>
-      <c r="AF9" s="1"/>
-      <c r="AG9" s="1"/>
-    </row>
-    <row r="10" ht="34.5" spans="1:33">
-      <c r="A10" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="L10" s="1">
-        <v>1</v>
-      </c>
-      <c r="M10" s="1">
-        <v>80</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="O10" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="Q10" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="R10" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="S10" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="T10" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="U10" s="1">
-        <v>100</v>
-      </c>
-      <c r="V10" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="W10" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="X10" s="1">
-        <v>95</v>
-      </c>
-      <c r="Y10" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="Z10" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="AA10" s="1">
-        <v>90</v>
-      </c>
-      <c r="AB10" s="1"/>
-      <c r="AC10" s="1"/>
-      <c r="AD10" s="1"/>
-      <c r="AE10" s="1"/>
-      <c r="AF10" s="1"/>
-      <c r="AG10" s="1"/>
-    </row>
-    <row r="11" ht="34.5" spans="1:33">
-      <c r="A11" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="L11" s="1">
-        <v>2</v>
-      </c>
-      <c r="M11" s="1">
-        <v>76</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="O11" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q11" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="R11" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="S11" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="T11" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="U11" s="1">
-        <v>100</v>
-      </c>
-      <c r="V11" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="W11" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="X11" s="1">
-        <v>90</v>
-      </c>
-      <c r="Y11" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="Z11" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="AA11" s="1">
-        <v>85</v>
-      </c>
-      <c r="AB11" s="1"/>
-      <c r="AC11" s="1"/>
-      <c r="AD11" s="1"/>
-      <c r="AE11" s="1"/>
-      <c r="AF11" s="1"/>
-      <c r="AG11" s="1"/>
-    </row>
-    <row r="12" ht="35" spans="1:33">
-      <c r="A12" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="L12" s="1">
-        <v>3</v>
-      </c>
-      <c r="M12" s="1">
-        <v>74</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="O12" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="P12" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="Q12" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="R12" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="S12" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="T12" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="U12" s="1">
-        <v>100</v>
-      </c>
-      <c r="V12" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="W12" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="X12" s="1">
-        <v>90</v>
-      </c>
-      <c r="Y12" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="Z12" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="AA12" s="1">
-        <v>85</v>
-      </c>
-      <c r="AB12" s="1"/>
-      <c r="AC12" s="1"/>
-      <c r="AD12" s="1"/>
-      <c r="AE12" s="1"/>
-      <c r="AF12" s="1"/>
-      <c r="AG12" s="1"/>
-    </row>
-    <row r="13" ht="57.5" spans="1:33">
-      <c r="A13" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="L13" s="1">
-        <v>4</v>
-      </c>
-      <c r="M13" s="1">
-        <v>86</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="O13" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="P13" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="Q13" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="R13" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="S13" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="T13" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U13" s="1">
-        <v>100</v>
-      </c>
-      <c r="V13" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="W13" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="X13" s="1">
-        <v>95</v>
-      </c>
-      <c r="Y13" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z13" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="AA13" s="1">
-        <v>90</v>
-      </c>
-      <c r="AB13" s="1"/>
-      <c r="AC13" s="1"/>
-      <c r="AD13" s="1"/>
-      <c r="AE13" s="1"/>
-      <c r="AF13" s="1"/>
-      <c r="AG13" s="1"/>
-    </row>
-    <row r="14" ht="34.5" spans="1:33">
-      <c r="A14" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="L14" s="1">
-        <v>5</v>
-      </c>
-      <c r="M14" s="1">
-        <v>35</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="O14" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="P14" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q14" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="R14" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="S14" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="T14" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U14" s="1">
-        <v>100</v>
-      </c>
-      <c r="V14" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="W14" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="X14" s="1">
-        <v>80</v>
-      </c>
-      <c r="Y14" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z14" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="AA14" s="1">
-        <v>75</v>
-      </c>
-      <c r="AB14" s="1"/>
-      <c r="AC14" s="1"/>
-      <c r="AD14" s="1"/>
-      <c r="AE14" s="1"/>
-      <c r="AF14" s="1"/>
-      <c r="AG14" s="1"/>
-    </row>
-    <row r="15" ht="34.5" spans="1:33">
-      <c r="A15" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="L15" s="1">
-        <v>6</v>
-      </c>
-      <c r="M15" s="1">
-        <v>68</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="O15" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="P15" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="Q15" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="R15" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="S15" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="T15" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="U15" s="1">
-        <v>100</v>
-      </c>
-      <c r="V15" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="W15" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="X15" s="1">
-        <v>90</v>
-      </c>
-      <c r="Y15" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z15" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="AA15" s="1">
-        <v>85</v>
-      </c>
-      <c r="AB15" s="1"/>
-      <c r="AC15" s="1"/>
-      <c r="AD15" s="1"/>
-      <c r="AE15" s="1"/>
-      <c r="AF15" s="1"/>
-      <c r="AG15" s="1"/>
-    </row>
-    <row r="16" ht="46" spans="1:33">
-      <c r="A16" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="L16" s="1">
-        <v>7</v>
-      </c>
-      <c r="M16" s="1">
-        <v>45</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="O16" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="P16" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="Q16" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="R16" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="S16" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="T16" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="U16" s="1">
-        <v>100</v>
-      </c>
-      <c r="V16" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="W16" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="X16" s="1">
-        <v>90</v>
-      </c>
-      <c r="Y16" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="Z16" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="AA16" s="1">
-        <v>85</v>
-      </c>
-      <c r="AB16" s="1"/>
-      <c r="AC16" s="1"/>
-      <c r="AD16" s="1"/>
-      <c r="AE16" s="1"/>
-      <c r="AF16" s="1"/>
-      <c r="AG16" s="1"/>
+      <c r="AB16" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>56</v>
+      </c>
+      <c r="AD16" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE16" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF16" t="s">
+        <v>56</v>
+      </c>
+      <c r="AG16" t="s">
+        <v>56</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:AG1" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:AG4 A6:K8 M6:AG9 A9:J9 A10:AG13 A14:K16 M14:AG16" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -5077,7 +4586,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -5086,16 +4595,16 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -5103,25 +4612,25 @@
         <v>49</v>
       </c>
       <c r="B2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -5129,25 +4638,25 @@
         <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -5155,51 +4664,51 @@
         <v>53</v>
       </c>
       <c r="B4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B5" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H5" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -5210,230 +4719,230 @@
         <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="B7" t="s">
         <v>54</v>
       </c>
       <c r="C7" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H7" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="B8" t="s">
         <v>54</v>
       </c>
       <c r="C8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D8" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E8" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F8" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="G8" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H8" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B9" t="s">
         <v>54</v>
       </c>
       <c r="C9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B10" t="s">
         <v>68</v>
       </c>
-      <c r="B10" t="s">
-        <v>67</v>
-      </c>
       <c r="C10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D11" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E11" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F11" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G11" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H11" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C12" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D12" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E12" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F12" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G12" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H12" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C13" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D13" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E13" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F13" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G13" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H13" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D14" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E14" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F14" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G14" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H14" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
   </sheetData>
@@ -5462,7 +4971,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -5471,790 +4980,790 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B2" t="s">
         <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B3" t="s">
         <v>49</v>
       </c>
       <c r="C3" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D3" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E3" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B4" t="s">
         <v>49</v>
       </c>
       <c r="C4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B5" t="s">
         <v>49</v>
       </c>
       <c r="C5" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D5" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E5" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F5" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B6" t="s">
         <v>49</v>
       </c>
       <c r="C6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B7" t="s">
         <v>51</v>
       </c>
       <c r="C7" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D7" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E7" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F7" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B8" t="s">
         <v>51</v>
       </c>
       <c r="C8" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D8" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E8" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F8" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B9" t="s">
         <v>51</v>
       </c>
       <c r="C9" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B10" t="s">
         <v>53</v>
       </c>
       <c r="C10" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B11" t="s">
         <v>53</v>
       </c>
       <c r="C11" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D11" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E11" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F11" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B12" t="s">
         <v>53</v>
       </c>
       <c r="C12" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D12" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E12" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F12" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B13" t="s">
         <v>53</v>
       </c>
       <c r="C13" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D13" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E13" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F13" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B14" t="s">
         <v>53</v>
       </c>
       <c r="C14" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D14" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E14" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F14" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B15" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C15" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D15" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E15" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F15" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B16" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C16" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D16" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E16" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F16" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B17" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C17" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D17" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E17" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F17" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B18" t="s">
         <v>55</v>
       </c>
       <c r="C18" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D18" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E18" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F18" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B19" t="s">
         <v>55</v>
       </c>
       <c r="C19" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D19" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E19" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F19" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B20" t="s">
         <v>55</v>
       </c>
       <c r="C20" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D20" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E20" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F20" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B21" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="C21" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D21" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E21" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F21" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B22" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="C22" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D22" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E22" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F22" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B23" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="C23" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D23" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E23" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F23" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B24" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="C24" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D24" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E24" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F24" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B25" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C25" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D25" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E25" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F25" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B26" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D26" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E26" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F26" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C27" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D27" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E27" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F27" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B28" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C28" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D28" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E28" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F28" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B29" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C29" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D29" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E29" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F29" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B30" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C30" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D30" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E30" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F30" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B31" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C31" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D31" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E31" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F31" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B32" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C32" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D32" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E32" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="F32" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B33" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C33" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D33" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E33" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="F33" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B34" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C34" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D34" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E34" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F34" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B35" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C35" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D35" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E35" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F35" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B36" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C36" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D36" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E36" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F36" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B37" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C37" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D37" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E37" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="F37" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B38" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C38" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D38" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E38" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="F38" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B39" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C39" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D39" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E39" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F39" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B40" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C40" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D40" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E40" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F40" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
   </sheetData>
@@ -6292,45 +5801,45 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="G1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B2" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D2" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="G2" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H2" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -6338,51 +5847,51 @@
         <v>54</v>
       </c>
       <c r="B3" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D3" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E3" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F3" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="G3" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H3" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B4" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C4" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D4" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E4" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F4" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="G4" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H4" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
   </sheetData>
@@ -6414,68 +5923,68 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B2" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E2">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="G2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B3" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C3" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D3" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E3">
         <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="G3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -6483,19 +5992,19 @@
         <v>40</v>
       </c>
       <c r="B4" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C4" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D4" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E4">
         <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="G4" t="s">
         <v>40</v>
@@ -6522,13 +6031,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -6536,10 +6045,10 @@
         <v>48</v>
       </c>
       <c r="B2" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C2" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6547,21 +6056,21 @@
         <v>50</v>
       </c>
       <c r="B3" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C3" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B4" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C4" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -6569,21 +6078,21 @@
         <v>54</v>
       </c>
       <c r="B5" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C5" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B6" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C6" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6591,87 +6100,87 @@
         <v>52</v>
       </c>
       <c r="B7" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C7" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="B8" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C8" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B9" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C9" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B10" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C10" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="B11" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C11" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B12" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C12" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B13" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C13" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B14" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C14" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
   </sheetData>
@@ -6695,222 +6204,222 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B2" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C2" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
+        <v>575</v>
+      </c>
+      <c r="B3" t="s">
         <v>574</v>
       </c>
-      <c r="B3" t="s">
-        <v>573</v>
-      </c>
       <c r="C3" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B4" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C4" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B5" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C5" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B6" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C6" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B7" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C7" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B8" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C8" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B9" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C9" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B10" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C10" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B11" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C11" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B12" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C12" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B13" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C13" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B14" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C14" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B15" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C15" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B16" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C16" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B17" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C17" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B18" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C18" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B19" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C19" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B20" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C20" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
   </sheetData>
